--- a/lab-standards/BRTC-lab-standard.xlsx
+++ b/lab-standards/BRTC-lab-standard.xlsx
@@ -556,6 +556,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -570,6 +574,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -639,7 +647,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -661,7 +671,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -683,7 +695,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -705,7 +719,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -727,7 +743,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>10</v>
       </c>
@@ -749,7 +767,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -771,7 +791,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -793,7 +815,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -815,7 +839,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -837,7 +863,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -859,7 +887,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -881,7 +911,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -903,7 +935,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -925,7 +959,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -947,7 +983,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -969,7 +1007,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -991,7 +1031,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -1013,7 +1055,9 @@
       <c r="C33" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>4</v>
       </c>
@@ -1035,7 +1079,9 @@
       <c r="C34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>
@@ -1057,7 +1103,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>3</v>
       </c>
